--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260630.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260630.xlsx
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>24,523,144</t>
+          <t>276,065,325</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>276,065,325</t>
+          <t>24,523,144</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,226,072</t>
+          <t>106,226,988</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>106,226,988</t>
+          <t>1,226,072</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
